--- a/research/traditional_assets/database/data/south_korea/south_korea_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0824</v>
+        <v>0.0858</v>
       </c>
       <c r="E2">
-        <v>0.148</v>
+        <v>0.136</v>
+      </c>
+      <c r="F2">
+        <v>0.09859999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>14048.7</v>
+        <v>13662</v>
       </c>
       <c r="L2">
-        <v>0.2704851277173756</v>
+        <v>0.3216313692992946</v>
       </c>
       <c r="M2">
-        <v>3493.8452</v>
+        <v>3254.9113</v>
       </c>
       <c r="N2">
-        <v>0.05838810928786414</v>
+        <v>0.05206150462648252</v>
       </c>
       <c r="O2">
-        <v>0.248695267177746</v>
+        <v>0.2382455936173328</v>
       </c>
       <c r="P2">
-        <v>2992.9822</v>
+        <v>2702.6113</v>
       </c>
       <c r="Q2">
-        <v>0.05001783473126743</v>
+        <v>0.04322760214649595</v>
       </c>
       <c r="R2">
-        <v>0.2130433563247845</v>
+        <v>0.1978195944956815</v>
       </c>
       <c r="S2">
-        <v>500.8629999999999</v>
+        <v>552.3000000000002</v>
       </c>
       <c r="T2">
-        <v>0.1433558075211804</v>
+        <v>0.1696820432556795</v>
       </c>
       <c r="U2">
-        <v>66562.89999999999</v>
+        <v>62510.48</v>
       </c>
       <c r="V2">
-        <v>1.112379529498666</v>
+        <v>0.9998397325677179</v>
       </c>
       <c r="W2">
-        <v>0.1029845702452048</v>
+        <v>0.08332936562629212</v>
       </c>
       <c r="X2">
-        <v>0.1902803066167651</v>
+        <v>0.2487062403442951</v>
       </c>
       <c r="Y2">
-        <v>-0.08729573637156034</v>
+        <v>-0.165376874718003</v>
       </c>
       <c r="Z2">
-        <v>0.08608189952998686</v>
+        <v>0.06641487806343965</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0409446090274151</v>
+        <v>0.06410830539979484</v>
       </c>
       <c r="AC2">
-        <v>-0.0409446090274151</v>
+        <v>-0.06410830539979484</v>
       </c>
       <c r="AD2">
-        <v>546392.4</v>
+        <v>570642.2000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>546392.4</v>
+        <v>570642.2000000001</v>
       </c>
       <c r="AG2">
-        <v>479829.5</v>
+        <v>508131.7200000001</v>
       </c>
       <c r="AH2">
-        <v>0.9012945071900845</v>
+        <v>0.9012568175604786</v>
       </c>
       <c r="AI2">
-        <v>0.7717558296695373</v>
+        <v>0.798496765389726</v>
       </c>
       <c r="AJ2">
-        <v>0.8891201216748524</v>
+        <v>0.8904402755149187</v>
       </c>
       <c r="AK2">
-        <v>0.7480700729253323</v>
+        <v>0.7791816518024669</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hana Financial Group Inc. (KOSE:A086790)</t>
+          <t>Woori Financial Group Inc. (KOSE:A316140)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0793</v>
+        <v>0.113</v>
       </c>
       <c r="E3">
-        <v>0.229</v>
+        <v>0.148</v>
+      </c>
+      <c r="F3">
+        <v>0.148</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2719.6</v>
+        <v>2125.2</v>
       </c>
       <c r="L3">
-        <v>0.1788857462342958</v>
+        <v>0.3031539306449082</v>
       </c>
       <c r="M3">
-        <v>504.468</v>
+        <v>944.4000000000001</v>
       </c>
       <c r="N3">
-        <v>0.04898413376575457</v>
+        <v>0.1419808767815263</v>
       </c>
       <c r="O3">
-        <v>0.1854934549198412</v>
+        <v>0.4443817052512706</v>
       </c>
       <c r="P3">
-        <v>504.468</v>
+        <v>496.6</v>
       </c>
       <c r="Q3">
-        <v>0.04898413376575457</v>
+        <v>0.07465872872692285</v>
       </c>
       <c r="R3">
-        <v>0.1854934549198412</v>
+        <v>0.2336721249764728</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>447.8000000000001</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.4741634900465905</v>
       </c>
       <c r="U3">
-        <v>19398.2</v>
+        <v>6460.2</v>
       </c>
       <c r="V3">
-        <v>1.883576408443866</v>
+        <v>0.9712249684286487</v>
       </c>
       <c r="W3">
-        <v>0.103604598892182</v>
+        <v>0.0992203184088893</v>
       </c>
       <c r="X3">
-        <v>0.2085332077915428</v>
+        <v>0.3218315933692606</v>
       </c>
       <c r="Y3">
-        <v>-0.1049286088993608</v>
+        <v>-0.2226112749603713</v>
       </c>
       <c r="Z3">
-        <v>0.1654773514916146</v>
+        <v>0.0955558221129337</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04069329366105783</v>
+        <v>0.06301421084335852</v>
       </c>
       <c r="AC3">
-        <v>-0.04069329366105783</v>
+        <v>-0.06301421084335852</v>
       </c>
       <c r="AD3">
-        <v>86351.10000000001</v>
+        <v>74819.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>86351.10000000001</v>
+        <v>74819.8</v>
       </c>
       <c r="AG3">
-        <v>66952.90000000001</v>
+        <v>68359.60000000001</v>
       </c>
       <c r="AH3">
-        <v>0.8934440562153839</v>
+        <v>0.9183566257606963</v>
       </c>
       <c r="AI3">
-        <v>0.7479530081879673</v>
+        <v>0.7753588194451642</v>
       </c>
       <c r="AJ3">
-        <v>0.8666873782386102</v>
+        <v>0.9113252420971801</v>
       </c>
       <c r="AK3">
-        <v>0.6970506508474082</v>
+        <v>0.7592406660387753</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Woori Financial Group Inc. (KOSE:A316140)</t>
+          <t>Hana Financial Group Inc. (KOSE:A086790)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.08550000000000001</v>
+        <v>-0.0215</v>
       </c>
       <c r="E4">
-        <v>0.123</v>
+        <v>0.178</v>
+      </c>
+      <c r="F4">
+        <v>0.0727</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2000.5</v>
+        <v>2572.3</v>
       </c>
       <c r="L4">
-        <v>0.2868552746669726</v>
+        <v>0.301888342507071</v>
       </c>
       <c r="M4">
-        <v>849.9</v>
+        <v>472</v>
       </c>
       <c r="N4">
-        <v>0.1094258970760535</v>
+        <v>0.04867033069014941</v>
       </c>
       <c r="O4">
-        <v>0.4248437890527368</v>
+        <v>0.1834933716907048</v>
       </c>
       <c r="P4">
-        <v>349.5</v>
+        <v>472</v>
       </c>
       <c r="Q4">
-        <v>0.04499864810928427</v>
+        <v>0.04867033069014941</v>
       </c>
       <c r="R4">
-        <v>0.1747063234191452</v>
+        <v>0.1834933716907048</v>
       </c>
       <c r="S4">
-        <v>500.4</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.5887751500176491</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>9371.1</v>
+        <v>23861.7</v>
       </c>
       <c r="V4">
-        <v>1.206543151064131</v>
+        <v>2.460501758112581</v>
       </c>
       <c r="W4">
-        <v>0.1023645415982275</v>
+        <v>0.09082851937119532</v>
       </c>
       <c r="X4">
-        <v>0.1995230297780329</v>
+        <v>0.2998608977886724</v>
       </c>
       <c r="Y4">
-        <v>-0.09715848817980542</v>
+        <v>-0.2090323784174771</v>
       </c>
       <c r="Z4">
-        <v>0.1151182810253498</v>
+        <v>0.08950117696983576</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04069901156099151</v>
+        <v>0.06305873295689013</v>
       </c>
       <c r="AC4">
-        <v>-0.04069901156099151</v>
+        <v>-0.06305873295689013</v>
       </c>
       <c r="AD4">
-        <v>61607.6</v>
+        <v>99614.10000000001</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>61607.6</v>
+        <v>99614.10000000001</v>
       </c>
       <c r="AG4">
-        <v>52236.5</v>
+        <v>75752.40000000001</v>
       </c>
       <c r="AH4">
-        <v>0.8880438777937139</v>
+        <v>0.9112823843676815</v>
       </c>
       <c r="AI4">
-        <v>0.7200194474766197</v>
+        <v>0.7941744863709929</v>
       </c>
       <c r="AJ4">
-        <v>0.8705590016565727</v>
+        <v>0.8865082978058592</v>
       </c>
       <c r="AK4">
-        <v>0.6855840520154818</v>
+        <v>0.745819849107949</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,10 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0757</v>
+        <v>0.0759</v>
       </c>
       <c r="E5">
-        <v>0.247</v>
+        <v>0.268</v>
+      </c>
+      <c r="F5">
+        <v>0.09859999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,28 +984,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>404.2</v>
+        <v>404.8</v>
       </c>
       <c r="L5">
-        <v>0.2597519439624703</v>
+        <v>0.2762762762762763</v>
       </c>
       <c r="M5">
-        <v>61.3988</v>
+        <v>81.0231</v>
       </c>
       <c r="N5">
-        <v>0.04504350377815274</v>
+        <v>0.06680113776898343</v>
       </c>
       <c r="O5">
-        <v>0.151902028698664</v>
+        <v>0.2001558794466403</v>
       </c>
       <c r="P5">
-        <v>61.3988</v>
+        <v>81.0231</v>
       </c>
       <c r="Q5">
-        <v>0.04504350377815274</v>
+        <v>0.06680113776898343</v>
       </c>
       <c r="R5">
-        <v>0.151902028698664</v>
+        <v>0.2001558794466403</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1002,55 +1014,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2346.2</v>
+        <v>1721.1</v>
       </c>
       <c r="V5">
-        <v>1.72122368131465</v>
+        <v>1.418995795201583</v>
       </c>
       <c r="W5">
-        <v>0.1269791404875597</v>
+        <v>0.1178011233012251</v>
       </c>
       <c r="X5">
-        <v>0.1677336089707719</v>
+        <v>0.2203549401470872</v>
       </c>
       <c r="Y5">
-        <v>-0.04075446848321215</v>
+        <v>-0.102553816845862</v>
       </c>
       <c r="Z5">
-        <v>0.1750551230706925</v>
+        <v>0.1514810028431119</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.040724822848517</v>
+        <v>0.06331377706528557</v>
       </c>
       <c r="AC5">
-        <v>-0.040724822848517</v>
+        <v>-0.06331377706528557</v>
       </c>
       <c r="AD5">
-        <v>8635.200000000001</v>
+        <v>8171.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>8635.200000000001</v>
+        <v>8171.8</v>
       </c>
       <c r="AG5">
-        <v>6289.000000000001</v>
+        <v>6450.700000000001</v>
       </c>
       <c r="AH5">
-        <v>0.8636668233599711</v>
+        <v>0.8707577226762709</v>
       </c>
       <c r="AI5">
-        <v>0.7070846025351282</v>
+        <v>0.7167239685658153</v>
       </c>
       <c r="AJ5">
-        <v>0.8218658930228304</v>
+        <v>0.8417323451119579</v>
       </c>
       <c r="AK5">
-        <v>0.6374287973079809</v>
+        <v>0.6663602086669078</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1076,10 +1088,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.026</v>
+        <v>0.0898</v>
       </c>
       <c r="E6">
-        <v>0.132</v>
+        <v>0.124</v>
+      </c>
+      <c r="F6">
+        <v>0.08210000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,28 +1109,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1839.4</v>
+        <v>1819.5</v>
       </c>
       <c r="L6">
-        <v>0.3058937005255106</v>
+        <v>0.3043812837713502</v>
       </c>
       <c r="M6">
-        <v>296.2314</v>
+        <v>432.9882</v>
       </c>
       <c r="N6">
-        <v>0.04600080749103219</v>
+        <v>0.06990332735990701</v>
       </c>
       <c r="O6">
-        <v>0.1610478416875068</v>
+        <v>0.2379709810387469</v>
       </c>
       <c r="P6">
-        <v>296.2314</v>
+        <v>432.9882</v>
       </c>
       <c r="Q6">
-        <v>0.04600080749103219</v>
+        <v>0.06990332735990701</v>
       </c>
       <c r="R6">
-        <v>0.1610478416875068</v>
+        <v>0.2379709810387469</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,55 +1139,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>17188.6</v>
+        <v>14658.1</v>
       </c>
       <c r="V6">
-        <v>2.669161606907154</v>
+        <v>2.366461632844158</v>
       </c>
       <c r="W6">
-        <v>0.08757296159815656</v>
+        <v>0.08163036407276969</v>
       </c>
       <c r="X6">
-        <v>0.5522908364948087</v>
+        <v>0.6450270473073849</v>
       </c>
       <c r="Y6">
-        <v>-0.4647178748966522</v>
+        <v>-0.5633966832346152</v>
       </c>
       <c r="Z6">
-        <v>0.03636823289410259</v>
+        <v>0.03501329025471133</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04116439520631321</v>
+        <v>0.06410830539979484</v>
       </c>
       <c r="AC6">
-        <v>-0.04116439520631321</v>
+        <v>-0.06410830539979484</v>
       </c>
       <c r="AD6">
-        <v>165211.2</v>
+        <v>158665.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>165211.2</v>
+        <v>158665.2</v>
       </c>
       <c r="AG6">
-        <v>148022.6</v>
+        <v>144007.1</v>
       </c>
       <c r="AH6">
-        <v>0.9624837387977575</v>
+        <v>0.9624279612979068</v>
       </c>
       <c r="AI6">
-        <v>0.8786493118600043</v>
+        <v>0.8899386273205457</v>
       </c>
       <c r="AJ6">
-        <v>0.9583089206880901</v>
+        <v>0.9587613148230506</v>
       </c>
       <c r="AK6">
-        <v>0.866439943807071</v>
+        <v>0.8800792276707712</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1198,10 +1213,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.153</v>
+        <v>0.0876</v>
       </c>
       <c r="E7">
-        <v>0.164</v>
+        <v>0.0775</v>
+      </c>
+      <c r="F7">
+        <v>0.08789999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1216,28 +1234,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3680.6</v>
+        <v>3248.7</v>
       </c>
       <c r="L7">
-        <v>0.3262798634812287</v>
+        <v>0.3503925967470555</v>
       </c>
       <c r="M7">
-        <v>882.5</v>
+        <v>205.6</v>
       </c>
       <c r="N7">
-        <v>0.04902478181888885</v>
+        <v>0.01375462445727436</v>
       </c>
       <c r="O7">
-        <v>0.2397706895614845</v>
+        <v>0.06328685320281958</v>
       </c>
       <c r="P7">
-        <v>882.5</v>
+        <v>205.6</v>
       </c>
       <c r="Q7">
-        <v>0.04902478181888885</v>
+        <v>0.01375462445727436</v>
       </c>
       <c r="R7">
-        <v>0.2397706895614845</v>
+        <v>0.06328685320281958</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1246,55 +1264,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>7331.5</v>
+        <v>6839.7</v>
       </c>
       <c r="V7">
-        <v>0.4072806661815112</v>
+        <v>0.4575754129397833</v>
       </c>
       <c r="W7">
-        <v>0.1039811508384939</v>
+        <v>0.08173405925448837</v>
       </c>
       <c r="X7">
-        <v>0.1663125602483708</v>
+        <v>0.2487062403442951</v>
       </c>
       <c r="Y7">
-        <v>-0.0623314094098769</v>
+        <v>-0.1669721810898067</v>
       </c>
       <c r="Z7">
-        <v>0.08070626297199086</v>
+        <v>0.0638685100608265</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.0427528322580886</v>
+        <v>0.06699972447380287</v>
       </c>
       <c r="AC7">
-        <v>-0.0427528322580886</v>
+        <v>-0.06699972447380287</v>
       </c>
       <c r="AD7">
-        <v>112751.3</v>
+        <v>119547.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>112751.3</v>
+        <v>119547.5</v>
       </c>
       <c r="AG7">
-        <v>105419.8</v>
+        <v>112707.8</v>
       </c>
       <c r="AH7">
-        <v>0.8623268100623775</v>
+        <v>0.8888607177059106</v>
       </c>
       <c r="AI7">
-        <v>0.7365206837446044</v>
+        <v>0.7768671357209744</v>
       </c>
       <c r="AJ7">
-        <v>0.8541486895655437</v>
+        <v>0.8829059460814458</v>
       </c>
       <c r="AK7">
-        <v>0.7232676225636325</v>
+        <v>0.7664882171643396</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1320,10 +1338,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0915</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E8">
-        <v>0.0941</v>
+        <v>0.0755</v>
+      </c>
+      <c r="F8">
+        <v>0.113</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1338,90 +1359,206 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3404.4</v>
+        <v>3325.3</v>
       </c>
       <c r="L8">
-        <v>0.3119810853906637</v>
+        <v>0.3488345257327487</v>
       </c>
       <c r="M8">
-        <v>899.347</v>
+        <v>1118.9</v>
       </c>
       <c r="N8">
-        <v>0.05631865688932863</v>
+        <v>0.07635978980413567</v>
       </c>
       <c r="O8">
-        <v>0.2641719539419575</v>
+        <v>0.3364809190148257</v>
       </c>
       <c r="P8">
-        <v>898.884</v>
+        <v>1014.4</v>
       </c>
       <c r="Q8">
-        <v>0.05628966303251946</v>
+        <v>0.06922814440728861</v>
       </c>
       <c r="R8">
-        <v>0.2640359534719774</v>
+        <v>0.3050551829910083</v>
       </c>
       <c r="S8">
-        <v>0.4629999999999654</v>
+        <v>104.5000000000001</v>
       </c>
       <c r="T8">
-        <v>0.0005148179734851681</v>
+        <v>0.09339529895433024</v>
       </c>
       <c r="U8">
-        <v>10927.3</v>
+        <v>8964.200000000001</v>
       </c>
       <c r="V8">
-        <v>0.6842863315569638</v>
+        <v>0.6117655087695353</v>
       </c>
       <c r="W8">
-        <v>0.09094211802921345</v>
+        <v>0.08332936562629212</v>
       </c>
       <c r="X8">
-        <v>0.1810375834554973</v>
+        <v>0.2373966874853532</v>
       </c>
       <c r="Y8">
-        <v>-0.09009546542628386</v>
+        <v>-0.1540673218590611</v>
       </c>
       <c r="Z8">
-        <v>0.0797042698559477</v>
+        <v>0.0676962976745243</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04276926505505525</v>
+        <v>0.06701300137085299</v>
       </c>
       <c r="AC8">
-        <v>-0.04276926505505525</v>
+        <v>-0.06701300137085299</v>
       </c>
       <c r="AD8">
-        <v>111836</v>
+        <v>109823.8</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>111836</v>
+        <v>109823.8</v>
       </c>
       <c r="AG8">
-        <v>100908.7</v>
+        <v>100859.6</v>
       </c>
       <c r="AH8">
-        <v>0.8750525214604449</v>
+        <v>0.8822832849173501</v>
       </c>
       <c r="AI8">
-        <v>0.7278857105665658</v>
+        <v>0.7561768602188444</v>
       </c>
       <c r="AJ8">
-        <v>0.8633707399878163</v>
+        <v>0.8731480375301049</v>
       </c>
       <c r="AK8">
-        <v>0.7070510525323768</v>
+        <v>0.7401376958041085</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KakaoBank Corp. (KOSE:A323410)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>0.3</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>166.2</v>
+      </c>
+      <c r="L9">
+        <v>0.2377342297239307</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>-0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>5.48</v>
+      </c>
+      <c r="V9">
+        <v>0.0005980378248011089</v>
+      </c>
+      <c r="W9">
+        <v>0.03585760517799352</v>
+      </c>
+      <c r="X9">
+        <v>0.06879393699109913</v>
+      </c>
+      <c r="Y9">
+        <v>-0.03293633181310561</v>
+      </c>
+      <c r="Z9">
+        <v>0.1510666067384653</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.06879393699109913</v>
+      </c>
+      <c r="AC9">
+        <v>-0.06879393699109913</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>-5.48</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.0005983956880567647</v>
+      </c>
+      <c r="AK9">
+        <v>-0.001404040973400085</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/south_korea/south_korea_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0858</v>
+        <v>0.08804999999999999</v>
       </c>
       <c r="E2">
-        <v>0.136</v>
+        <v>0.08385000000000001</v>
       </c>
       <c r="F2">
-        <v>0.09859999999999999</v>
+        <v>0.046</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>13662</v>
+        <v>14401.2</v>
       </c>
       <c r="L2">
-        <v>0.3216313692992946</v>
+        <v>0.1560789303414918</v>
       </c>
       <c r="M2">
-        <v>3254.9113</v>
+        <v>5990.7742</v>
       </c>
       <c r="N2">
-        <v>0.05206150462648252</v>
+        <v>0.08705837679634605</v>
       </c>
       <c r="O2">
-        <v>0.2382455936173328</v>
+        <v>0.4159913201677637</v>
       </c>
       <c r="P2">
-        <v>2702.6113</v>
+        <v>4342.8142</v>
       </c>
       <c r="Q2">
-        <v>0.04322760214649595</v>
+        <v>0.06311009935579313</v>
       </c>
       <c r="R2">
-        <v>0.1978195944956815</v>
+        <v>0.3015591895119851</v>
       </c>
       <c r="S2">
-        <v>552.3000000000002</v>
+        <v>1647.96</v>
       </c>
       <c r="T2">
-        <v>0.1696820432556795</v>
+        <v>0.2750829767544903</v>
       </c>
       <c r="U2">
-        <v>62510.48</v>
+        <v>79756.90000000001</v>
       </c>
       <c r="V2">
-        <v>0.9998397325677179</v>
+        <v>1.159033210149782</v>
       </c>
       <c r="W2">
-        <v>0.08332936562629212</v>
+        <v>0.1086515829174748</v>
       </c>
       <c r="X2">
-        <v>0.2487062403442951</v>
+        <v>0.1741941301106248</v>
       </c>
       <c r="Y2">
-        <v>-0.165376874718003</v>
+        <v>-0.06554254719314995</v>
       </c>
       <c r="Z2">
-        <v>0.06641487806343965</v>
+        <v>0.1428196579455826</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06410830539979484</v>
+        <v>0.05484660521633881</v>
       </c>
       <c r="AC2">
-        <v>-0.06410830539979484</v>
+        <v>-0.05484660521633881</v>
       </c>
       <c r="AD2">
-        <v>570642.2000000001</v>
+        <v>579810</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>570642.2000000001</v>
+        <v>579810</v>
       </c>
       <c r="AG2">
-        <v>508131.7200000001</v>
+        <v>500053.1</v>
       </c>
       <c r="AH2">
-        <v>0.9012568175604786</v>
+        <v>0.8939086832064157</v>
       </c>
       <c r="AI2">
-        <v>0.798496765389726</v>
+        <v>0.7715600267473078</v>
       </c>
       <c r="AJ2">
-        <v>0.8904402755149187</v>
+        <v>0.8790343391699702</v>
       </c>
       <c r="AK2">
-        <v>0.7791816518024669</v>
+        <v>0.7444361539604413</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Woori Financial Group Inc. (KOSE:A316140)</t>
+          <t>Hana Financial Group Inc. (KOSE:A086790)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.113</v>
+        <v>0.257</v>
       </c>
       <c r="E3">
-        <v>0.148</v>
+        <v>0.08990000000000001</v>
       </c>
       <c r="F3">
-        <v>0.148</v>
+        <v>0.046</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2125.2</v>
+        <v>2728.1</v>
       </c>
       <c r="L3">
-        <v>0.3031539306449082</v>
+        <v>0.1509380722904898</v>
       </c>
       <c r="M3">
-        <v>944.4000000000001</v>
+        <v>1041.64</v>
       </c>
       <c r="N3">
-        <v>0.1419808767815263</v>
+        <v>0.1072484658786706</v>
       </c>
       <c r="O3">
-        <v>0.4443817052512706</v>
+        <v>0.3818188482826876</v>
       </c>
       <c r="P3">
-        <v>496.6</v>
+        <v>930.24</v>
       </c>
       <c r="Q3">
-        <v>0.07465872872692285</v>
+        <v>0.09577859231497879</v>
       </c>
       <c r="R3">
-        <v>0.2336721249764728</v>
+        <v>0.340984568014369</v>
       </c>
       <c r="S3">
-        <v>447.8000000000001</v>
+        <v>111.4000000000001</v>
       </c>
       <c r="T3">
-        <v>0.4741634900465905</v>
+        <v>0.1069467378364887</v>
       </c>
       <c r="U3">
-        <v>6460.2</v>
+        <v>17155</v>
       </c>
       <c r="V3">
-        <v>0.9712249684286487</v>
+        <v>1.766298752110704</v>
       </c>
       <c r="W3">
-        <v>0.0992203184088893</v>
+        <v>0.1086515829174748</v>
       </c>
       <c r="X3">
-        <v>0.3218315933692606</v>
+        <v>0.2212294052119772</v>
       </c>
       <c r="Y3">
-        <v>-0.2226112749603713</v>
+        <v>-0.1125778222945024</v>
       </c>
       <c r="Z3">
-        <v>0.0955558221129337</v>
+        <v>0.179310488507315</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06301421084335852</v>
+        <v>0.0540792702093227</v>
       </c>
       <c r="AC3">
-        <v>-0.06301421084335852</v>
+        <v>-0.0540792702093227</v>
       </c>
       <c r="AD3">
-        <v>74819.8</v>
+        <v>99819.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>74819.8</v>
+        <v>99819.7</v>
       </c>
       <c r="AG3">
-        <v>68359.60000000001</v>
+        <v>82664.7</v>
       </c>
       <c r="AH3">
-        <v>0.9183566257606963</v>
+        <v>0.911328277281272</v>
       </c>
       <c r="AI3">
-        <v>0.7753588194451642</v>
+        <v>0.7688137342493607</v>
       </c>
       <c r="AJ3">
-        <v>0.9113252420971801</v>
+        <v>0.8948613888073993</v>
       </c>
       <c r="AK3">
-        <v>0.7592406660387753</v>
+        <v>0.7336170250530257</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hana Financial Group Inc. (KOSE:A086790)</t>
+          <t>Woori Financial Group Inc. (KOSE:A316140)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0215</v>
+        <v>0.0876</v>
       </c>
       <c r="E4">
-        <v>0.178</v>
+        <v>0.0745</v>
       </c>
       <c r="F4">
-        <v>0.0727</v>
+        <v>-0.00725</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2572.3</v>
+        <v>2167.7</v>
       </c>
       <c r="L4">
-        <v>0.301888342507071</v>
+        <v>0.2904634927441075</v>
       </c>
       <c r="M4">
-        <v>472</v>
+        <v>1476.8</v>
       </c>
       <c r="N4">
-        <v>0.04867033069014941</v>
+        <v>0.1978192729123691</v>
       </c>
       <c r="O4">
-        <v>0.1834933716907048</v>
+        <v>0.6812750841906169</v>
       </c>
       <c r="P4">
-        <v>472</v>
+        <v>699.6</v>
       </c>
       <c r="Q4">
-        <v>0.04867033069014941</v>
+        <v>0.09371232619819435</v>
       </c>
       <c r="R4">
-        <v>0.1834933716907048</v>
+        <v>0.3227383863080685</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>777.2000000000002</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.526273022751896</v>
       </c>
       <c r="U4">
-        <v>23861.7</v>
+        <v>7157.9</v>
       </c>
       <c r="V4">
-        <v>2.460501758112581</v>
+        <v>0.9588099766924746</v>
       </c>
       <c r="W4">
-        <v>0.09082851937119532</v>
+        <v>0.1101781493811787</v>
       </c>
       <c r="X4">
-        <v>0.2998608977886724</v>
+        <v>0.1954208365375864</v>
       </c>
       <c r="Y4">
-        <v>-0.2090323784174771</v>
+        <v>-0.08524268715640776</v>
       </c>
       <c r="Z4">
-        <v>0.08950117696983576</v>
+        <v>0.08506164002589608</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06305873295689013</v>
+        <v>0.05417332397313809</v>
       </c>
       <c r="AC4">
-        <v>-0.06305873295689013</v>
+        <v>-0.05417332397313809</v>
       </c>
       <c r="AD4">
-        <v>99614.10000000001</v>
+        <v>64463.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>99614.10000000001</v>
+        <v>64463.3</v>
       </c>
       <c r="AG4">
-        <v>75752.40000000001</v>
+        <v>57305.4</v>
       </c>
       <c r="AH4">
-        <v>0.9112823843676815</v>
+        <v>0.8962111090566075</v>
       </c>
       <c r="AI4">
-        <v>0.7941744863709929</v>
+        <v>0.7231553807028585</v>
       </c>
       <c r="AJ4">
-        <v>0.8865082978058592</v>
+        <v>0.8847412723017162</v>
       </c>
       <c r="AK4">
-        <v>0.745819849107949</v>
+        <v>0.6989844335100349</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0759</v>
+        <v>0.0617</v>
       </c>
       <c r="E5">
-        <v>0.268</v>
+        <v>0.219</v>
       </c>
       <c r="F5">
-        <v>0.09859999999999999</v>
+        <v>0.0771</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,28 +984,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>404.8</v>
+        <v>451.2</v>
       </c>
       <c r="L5">
-        <v>0.2762762762762763</v>
+        <v>0.2856419346670043</v>
       </c>
       <c r="M5">
-        <v>81.0231</v>
+        <v>120.528</v>
       </c>
       <c r="N5">
-        <v>0.06680113776898343</v>
+        <v>0.07006219845375806</v>
       </c>
       <c r="O5">
-        <v>0.2001558794466403</v>
+        <v>0.2671276595744681</v>
       </c>
       <c r="P5">
-        <v>81.0231</v>
+        <v>120.528</v>
       </c>
       <c r="Q5">
-        <v>0.06680113776898343</v>
+        <v>0.07006219845375806</v>
       </c>
       <c r="R5">
-        <v>0.2001558794466403</v>
+        <v>0.2671276595744681</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1014,55 +1014,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1721.1</v>
+        <v>1317.7</v>
       </c>
       <c r="V5">
-        <v>1.418995795201583</v>
+        <v>0.7659710515607744</v>
       </c>
       <c r="W5">
-        <v>0.1178011233012251</v>
+        <v>0.1458730723222657</v>
       </c>
       <c r="X5">
-        <v>0.2203549401470872</v>
+        <v>0.144124932765662</v>
       </c>
       <c r="Y5">
-        <v>-0.102553816845862</v>
+        <v>0.001748139556603662</v>
       </c>
       <c r="Z5">
-        <v>0.1514810028431119</v>
+        <v>0.166498018382663</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06331377706528557</v>
+        <v>0.05450427132808321</v>
       </c>
       <c r="AC5">
-        <v>-0.06331377706528557</v>
+        <v>-0.05450427132808321</v>
       </c>
       <c r="AD5">
-        <v>8171.8</v>
+        <v>9238.299999999999</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>8171.8</v>
+        <v>9238.299999999999</v>
       </c>
       <c r="AG5">
-        <v>6450.700000000001</v>
+        <v>7920.599999999999</v>
       </c>
       <c r="AH5">
-        <v>0.8707577226762709</v>
+        <v>0.8430182687569581</v>
       </c>
       <c r="AI5">
-        <v>0.7167239685658153</v>
+        <v>0.7078831624599635</v>
       </c>
       <c r="AJ5">
-        <v>0.8417323451119579</v>
+        <v>0.8215623022746839</v>
       </c>
       <c r="AK5">
-        <v>0.6663602086669078</v>
+        <v>0.6750760681502441</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0898</v>
+        <v>0.0885</v>
       </c>
       <c r="E6">
-        <v>0.124</v>
+        <v>0.117</v>
       </c>
       <c r="F6">
-        <v>0.08210000000000001</v>
+        <v>0.0328</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,28 +1109,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1819.5</v>
+        <v>2204.8</v>
       </c>
       <c r="L6">
-        <v>0.3043812837713502</v>
+        <v>0.3111399621800119</v>
       </c>
       <c r="M6">
-        <v>432.9882</v>
+        <v>568.5462</v>
       </c>
       <c r="N6">
-        <v>0.06990332735990701</v>
+        <v>0.07736901408450704</v>
       </c>
       <c r="O6">
-        <v>0.2379709810387469</v>
+        <v>0.2578674709724238</v>
       </c>
       <c r="P6">
-        <v>432.9882</v>
+        <v>568.5462</v>
       </c>
       <c r="Q6">
-        <v>0.06990332735990701</v>
+        <v>0.07736901408450704</v>
       </c>
       <c r="R6">
-        <v>0.2379709810387469</v>
+        <v>0.2578674709724238</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1139,55 +1139,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>14658.1</v>
+        <v>10521.1</v>
       </c>
       <c r="V6">
-        <v>2.366461632844158</v>
+        <v>1.431734367558005</v>
       </c>
       <c r="W6">
-        <v>0.08163036407276969</v>
+        <v>0.1149944453426937</v>
       </c>
       <c r="X6">
-        <v>0.6450270473073849</v>
+        <v>0.4448605010984245</v>
       </c>
       <c r="Y6">
-        <v>-0.5633966832346152</v>
+        <v>-0.3298660557557307</v>
       </c>
       <c r="Z6">
-        <v>0.03501329025471133</v>
+        <v>0.04333502730225358</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06410830539979484</v>
+        <v>0.05484660521633881</v>
       </c>
       <c r="AC6">
-        <v>-0.06410830539979484</v>
+        <v>-0.05484660521633881</v>
       </c>
       <c r="AD6">
-        <v>158665.2</v>
+        <v>180117.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>158665.2</v>
+        <v>180117.3</v>
       </c>
       <c r="AG6">
-        <v>144007.1</v>
+        <v>169596.2</v>
       </c>
       <c r="AH6">
-        <v>0.9624279612979068</v>
+        <v>0.9608008500750537</v>
       </c>
       <c r="AI6">
-        <v>0.8899386273205457</v>
+        <v>0.8863185440774414</v>
       </c>
       <c r="AJ6">
-        <v>0.9587613148230506</v>
+        <v>0.9584700756790115</v>
       </c>
       <c r="AK6">
-        <v>0.8800792276707712</v>
+        <v>0.8801116770498992</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0876</v>
+        <v>0.0594</v>
       </c>
       <c r="E7">
-        <v>0.0775</v>
+        <v>0.0667</v>
       </c>
       <c r="F7">
-        <v>0.08789999999999999</v>
+        <v>0.128</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1234,85 +1234,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3248.7</v>
+        <v>3511.4</v>
       </c>
       <c r="L7">
-        <v>0.3503925967470555</v>
+        <v>0.3293749061984091</v>
       </c>
       <c r="M7">
-        <v>205.6</v>
+        <v>1265</v>
       </c>
       <c r="N7">
-        <v>0.01375462445727436</v>
+        <v>0.07900670151705358</v>
       </c>
       <c r="O7">
-        <v>0.06328685320281958</v>
+        <v>0.36025516887851</v>
       </c>
       <c r="P7">
-        <v>205.6</v>
+        <v>987.4</v>
       </c>
       <c r="Q7">
-        <v>0.01375462445727436</v>
+        <v>0.06166894630667091</v>
       </c>
       <c r="R7">
-        <v>0.06328685320281958</v>
+        <v>0.2811983824115737</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>277.6</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.2194466403162056</v>
       </c>
       <c r="U7">
-        <v>6839.7</v>
+        <v>20768.4</v>
       </c>
       <c r="V7">
-        <v>0.4575754129397833</v>
+        <v>1.297108916827491</v>
       </c>
       <c r="W7">
-        <v>0.08173405925448837</v>
+        <v>0.1055637895217853</v>
       </c>
       <c r="X7">
-        <v>0.2487062403442951</v>
+        <v>0.1741941301106248</v>
       </c>
       <c r="Y7">
-        <v>-0.1669721810898067</v>
+        <v>-0.0686303405888395</v>
       </c>
       <c r="Z7">
-        <v>0.0638685100608265</v>
+        <v>0.07303363474002732</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06699972447380287</v>
+        <v>0.05723105259778904</v>
       </c>
       <c r="AC7">
-        <v>-0.06699972447380287</v>
+        <v>-0.05723105259778904</v>
       </c>
       <c r="AD7">
-        <v>119547.5</v>
+        <v>116625.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>119547.5</v>
+        <v>116625.5</v>
       </c>
       <c r="AG7">
-        <v>112707.8</v>
+        <v>95857.10000000001</v>
       </c>
       <c r="AH7">
-        <v>0.8888607177059106</v>
+        <v>0.8792846329223867</v>
       </c>
       <c r="AI7">
-        <v>0.7768671357209744</v>
+        <v>0.7273501181841427</v>
       </c>
       <c r="AJ7">
-        <v>0.8829059460814458</v>
+        <v>0.8568737909901277</v>
       </c>
       <c r="AK7">
-        <v>0.7664882171643396</v>
+        <v>0.686780402738034</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1338,13 +1338,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.08400000000000001</v>
+        <v>0.453</v>
       </c>
       <c r="E8">
-        <v>0.0755</v>
+        <v>0.07780000000000001</v>
       </c>
       <c r="F8">
-        <v>0.113</v>
+        <v>0.0373</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1359,85 +1359,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3325.3</v>
+        <v>3085.6</v>
       </c>
       <c r="L8">
-        <v>0.3488345257327487</v>
+        <v>0.06641297610028238</v>
       </c>
       <c r="M8">
-        <v>1118.9</v>
+        <v>1508.6</v>
       </c>
       <c r="N8">
-        <v>0.07635978980413567</v>
+        <v>0.09431048818149423</v>
       </c>
       <c r="O8">
-        <v>0.3364809190148257</v>
+        <v>0.4889162561576355</v>
       </c>
       <c r="P8">
-        <v>1014.4</v>
+        <v>1036.5</v>
       </c>
       <c r="Q8">
-        <v>0.06922814440728861</v>
+        <v>0.06479704427954314</v>
       </c>
       <c r="R8">
-        <v>0.3050551829910083</v>
+        <v>0.3359152190821882</v>
       </c>
       <c r="S8">
-        <v>104.5000000000001</v>
+        <v>472.0999999999999</v>
       </c>
       <c r="T8">
-        <v>0.09339529895433024</v>
+        <v>0.312939148879756</v>
       </c>
       <c r="U8">
-        <v>8964.200000000001</v>
+        <v>22821</v>
       </c>
       <c r="V8">
-        <v>0.6117655087695353</v>
+        <v>1.426660248435556</v>
       </c>
       <c r="W8">
-        <v>0.08332936562629212</v>
+        <v>0.09135994741532713</v>
       </c>
       <c r="X8">
-        <v>0.2373966874853532</v>
+        <v>0.1673490487586974</v>
       </c>
       <c r="Y8">
-        <v>-0.1540673218590611</v>
+        <v>-0.07598910134337025</v>
       </c>
       <c r="Z8">
-        <v>0.0676962976745243</v>
+        <v>0.3450904194120789</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06701300137085299</v>
+        <v>0.05725024348008073</v>
       </c>
       <c r="AC8">
-        <v>-0.06701300137085299</v>
+        <v>-0.05725024348008073</v>
       </c>
       <c r="AD8">
-        <v>109823.8</v>
+        <v>109545.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>109823.8</v>
+        <v>109545.9</v>
       </c>
       <c r="AG8">
-        <v>100859.6</v>
+        <v>86724.89999999999</v>
       </c>
       <c r="AH8">
-        <v>0.8822832849173501</v>
+        <v>0.8725836771757658</v>
       </c>
       <c r="AI8">
-        <v>0.7561768602188444</v>
+        <v>0.7232905637255711</v>
       </c>
       <c r="AJ8">
-        <v>0.8731480375301049</v>
+        <v>0.8442762434166333</v>
       </c>
       <c r="AK8">
-        <v>0.7401376958041085</v>
+        <v>0.674199413995844</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F9">
-        <v>0.3</v>
+        <v>0.373</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1478,19 +1478,19 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>166.2</v>
+        <v>252.4</v>
       </c>
       <c r="L9">
-        <v>0.2377342297239307</v>
+        <v>0.2673445609575257</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>9.66</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.0009148333696362449</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.03827258320126783</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1502,34 +1502,37 @@
         <v>-0</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>9.66</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
       </c>
       <c r="U9">
-        <v>5.48</v>
+        <v>15.8</v>
       </c>
       <c r="V9">
-        <v>0.0005980378248011089</v>
+        <v>0.001496311308514769</v>
       </c>
       <c r="W9">
-        <v>0.03585760517799352</v>
+        <v>0.06457720353076628</v>
       </c>
       <c r="X9">
-        <v>0.06879393699109913</v>
+        <v>0.05974923784319833</v>
       </c>
       <c r="Y9">
-        <v>-0.03293633181310561</v>
+        <v>0.004827965687567951</v>
       </c>
       <c r="Z9">
-        <v>0.1510666067384653</v>
+        <v>0.2418896136837628</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06879393699109913</v>
+        <v>0.05974923784319833</v>
       </c>
       <c r="AC9">
-        <v>-0.06879393699109913</v>
+        <v>-0.05974923784319833</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -1541,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>-5.48</v>
+        <v>-15.8</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -1550,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="AJ9">
-        <v>-0.0005983956880567647</v>
+        <v>-0.001498553611229668</v>
       </c>
       <c r="AK9">
-        <v>-0.001404040973400085</v>
+        <v>-0.003577979573812813</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/research/traditional_assets/database/data/south_korea/south_korea_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08804999999999999</v>
+        <v>0.0623</v>
       </c>
       <c r="E2">
-        <v>0.08385000000000001</v>
+        <v>0.09390000000000001</v>
       </c>
       <c r="F2">
-        <v>0.046</v>
+        <v>0.09759999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>14401.2</v>
+        <v>9130.299999999999</v>
       </c>
       <c r="L2">
-        <v>0.1560789303414918</v>
+        <v>0.3168416815307843</v>
       </c>
       <c r="M2">
-        <v>5990.7742</v>
+        <v>4120.0526</v>
       </c>
       <c r="N2">
-        <v>0.08705837679634605</v>
+        <v>0.09156791607863184</v>
       </c>
       <c r="O2">
-        <v>0.4159913201677637</v>
+        <v>0.4512505175076394</v>
       </c>
       <c r="P2">
-        <v>4342.8142</v>
+        <v>2758.5526</v>
       </c>
       <c r="Q2">
-        <v>0.06311009935579313</v>
+        <v>0.06130866216982075</v>
       </c>
       <c r="R2">
-        <v>0.3015591895119851</v>
+        <v>0.3021316495624459</v>
       </c>
       <c r="S2">
-        <v>1647.96</v>
+        <v>1361.5</v>
       </c>
       <c r="T2">
-        <v>0.2750829767544903</v>
+        <v>0.330456946107921</v>
       </c>
       <c r="U2">
-        <v>79756.90000000001</v>
+        <v>58529.3</v>
       </c>
       <c r="V2">
-        <v>1.159033210149782</v>
+        <v>1.300810099012102</v>
       </c>
       <c r="W2">
-        <v>0.1086515829174748</v>
+        <v>0.08781607232975217</v>
       </c>
       <c r="X2">
-        <v>0.1741941301106248</v>
+        <v>0.1746496738443003</v>
       </c>
       <c r="Y2">
-        <v>-0.06554254719314995</v>
+        <v>-0.08683360151454811</v>
       </c>
       <c r="Z2">
-        <v>0.1428196579455826</v>
+        <v>0.06302290634614068</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05484660521633881</v>
+        <v>0.05987982846021396</v>
       </c>
       <c r="AC2">
-        <v>-0.05484660521633881</v>
+        <v>-0.05987982846021396</v>
       </c>
       <c r="AD2">
-        <v>579810</v>
+        <v>424344.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>579810</v>
+        <v>424344.3</v>
       </c>
       <c r="AG2">
-        <v>500053.1</v>
+        <v>365815</v>
       </c>
       <c r="AH2">
-        <v>0.8939086832064157</v>
+        <v>0.9041321535743476</v>
       </c>
       <c r="AI2">
-        <v>0.7715600267473078</v>
+        <v>0.7852675645256741</v>
       </c>
       <c r="AJ2">
-        <v>0.8790343391699702</v>
+        <v>0.8904735649978883</v>
       </c>
       <c r="AK2">
-        <v>0.7444361539604413</v>
+        <v>0.7591846052474565</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hana Financial Group Inc. (KOSE:A086790)</t>
+          <t>Industrial Bank of Korea (KOSE:A024110)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.257</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="E3">
-        <v>0.08990000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="F3">
-        <v>0.046</v>
+        <v>0.015</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2728.1</v>
+        <v>2091.8</v>
       </c>
       <c r="L3">
-        <v>0.1509380722904898</v>
+        <v>0.3120273273766017</v>
       </c>
       <c r="M3">
-        <v>1041.64</v>
+        <v>597.2526</v>
       </c>
       <c r="N3">
-        <v>0.1072484658786706</v>
+        <v>0.07720232155321735</v>
       </c>
       <c r="O3">
-        <v>0.3818188482826876</v>
+        <v>0.2855208910985754</v>
       </c>
       <c r="P3">
-        <v>930.24</v>
+        <v>597.2526</v>
       </c>
       <c r="Q3">
-        <v>0.09577859231497879</v>
+        <v>0.07720232155321735</v>
       </c>
       <c r="R3">
-        <v>0.340984568014369</v>
+        <v>0.2855208910985754</v>
       </c>
       <c r="S3">
-        <v>111.4000000000001</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.1069467378364887</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>17155</v>
+        <v>11575.8</v>
       </c>
       <c r="V3">
-        <v>1.766298752110704</v>
+        <v>1.496316020785398</v>
       </c>
       <c r="W3">
-        <v>0.1086515829174748</v>
+        <v>0.09170458829821747</v>
       </c>
       <c r="X3">
-        <v>0.2212294052119772</v>
+        <v>0.4263406632787151</v>
       </c>
       <c r="Y3">
-        <v>-0.1125778222945024</v>
+        <v>-0.3346360749804976</v>
       </c>
       <c r="Z3">
-        <v>0.179310488507315</v>
+        <v>0.03481225301573949</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0540792702093227</v>
+        <v>0.05829540398678958</v>
       </c>
       <c r="AC3">
-        <v>-0.0540792702093227</v>
+        <v>-0.05829540398678958</v>
       </c>
       <c r="AD3">
-        <v>99819.7</v>
+        <v>189456</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>99819.7</v>
+        <v>189456</v>
       </c>
       <c r="AG3">
-        <v>82664.7</v>
+        <v>177880.2</v>
       </c>
       <c r="AH3">
-        <v>0.911328277281272</v>
+        <v>0.9607682251123523</v>
       </c>
       <c r="AI3">
-        <v>0.7688137342493607</v>
+        <v>0.8806356923892151</v>
       </c>
       <c r="AJ3">
-        <v>0.8948613888073993</v>
+        <v>0.9583215707232765</v>
       </c>
       <c r="AK3">
-        <v>0.7336170250530257</v>
+        <v>0.8738478195831493</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Woori Financial Group Inc. (KOSE:A316140)</t>
+          <t>Shinhan Financial Group Co., Ltd. (KOSE:A055550)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0876</v>
+        <v>0.0599</v>
       </c>
       <c r="E4">
-        <v>0.0745</v>
+        <v>0.06150000000000001</v>
       </c>
       <c r="F4">
-        <v>-0.00725</v>
+        <v>0.09759999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2167.7</v>
+        <v>3497.6</v>
       </c>
       <c r="L4">
-        <v>0.2904634927441075</v>
+        <v>0.3076138292539203</v>
       </c>
       <c r="M4">
-        <v>1476.8</v>
+        <v>1529.3</v>
       </c>
       <c r="N4">
-        <v>0.1978192729123691</v>
+        <v>0.09416466039025412</v>
       </c>
       <c r="O4">
-        <v>0.6812750841906169</v>
+        <v>0.437242680695334</v>
       </c>
       <c r="P4">
-        <v>699.6</v>
+        <v>958.1</v>
       </c>
       <c r="Q4">
-        <v>0.09371232619819435</v>
+        <v>0.05899376258412507</v>
       </c>
       <c r="R4">
-        <v>0.3227383863080685</v>
+        <v>0.2739306953339433</v>
       </c>
       <c r="S4">
-        <v>777.2000000000002</v>
+        <v>571.2000000000002</v>
       </c>
       <c r="T4">
-        <v>0.526273022751896</v>
+        <v>0.3735042176159027</v>
       </c>
       <c r="U4">
-        <v>7157.9</v>
+        <v>30114.5</v>
       </c>
       <c r="V4">
-        <v>0.9588099766924746</v>
+        <v>1.854261207952859</v>
       </c>
       <c r="W4">
-        <v>0.1101781493811787</v>
+        <v>0.08781607232975217</v>
       </c>
       <c r="X4">
-        <v>0.1954208365375864</v>
+        <v>0.1746496738443003</v>
       </c>
       <c r="Y4">
-        <v>-0.08524268715640776</v>
+        <v>-0.08683360151454811</v>
       </c>
       <c r="Z4">
-        <v>0.08506164002589608</v>
+        <v>0.0898441450895115</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05417332397313809</v>
+        <v>0.05987982846021396</v>
       </c>
       <c r="AC4">
-        <v>-0.05417332397313809</v>
+        <v>-0.05987982846021396</v>
       </c>
       <c r="AD4">
-        <v>64463.3</v>
+        <v>120346.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>64463.3</v>
+        <v>120346.8</v>
       </c>
       <c r="AG4">
-        <v>57305.4</v>
+        <v>90232.3</v>
       </c>
       <c r="AH4">
-        <v>0.8962111090566075</v>
+        <v>0.8810967328635491</v>
       </c>
       <c r="AI4">
-        <v>0.7231553807028585</v>
+        <v>0.7289738307487944</v>
       </c>
       <c r="AJ4">
-        <v>0.8847412723017162</v>
+        <v>0.8474664938529017</v>
       </c>
       <c r="AK4">
-        <v>0.6989844335100349</v>
+        <v>0.6685052624092247</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JB Financial Group Co., Ltd. (KOSE:A175330)</t>
+          <t>KB Financial Group Inc. (KOSE:A105560)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0617</v>
+        <v>0.0623</v>
       </c>
       <c r="E5">
-        <v>0.219</v>
+        <v>0.09390000000000001</v>
       </c>
       <c r="F5">
-        <v>0.0771</v>
+        <v>0.122</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,584 +984,90 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>451.2</v>
+        <v>3540.9</v>
       </c>
       <c r="L5">
-        <v>0.2856419346670043</v>
+        <v>0.3296129428629941</v>
       </c>
       <c r="M5">
-        <v>120.528</v>
+        <v>1993.5</v>
       </c>
       <c r="N5">
-        <v>0.07006219845375806</v>
+        <v>0.09484907886723509</v>
       </c>
       <c r="O5">
-        <v>0.2671276595744681</v>
+        <v>0.5629924595441836</v>
       </c>
       <c r="P5">
-        <v>120.528</v>
+        <v>1203.2</v>
       </c>
       <c r="Q5">
-        <v>0.07006219845375806</v>
+        <v>0.05724725943970768</v>
       </c>
       <c r="R5">
-        <v>0.2671276595744681</v>
+        <v>0.3398006156626847</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>790.3</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.3964384248808628</v>
       </c>
       <c r="U5">
-        <v>1317.7</v>
+        <v>16839</v>
       </c>
       <c r="V5">
-        <v>0.7659710515607744</v>
+        <v>0.8011856729598051</v>
       </c>
       <c r="W5">
-        <v>0.1458730723222657</v>
+        <v>0.08379559072708513</v>
       </c>
       <c r="X5">
-        <v>0.144124932765662</v>
+        <v>0.1457599788165728</v>
       </c>
       <c r="Y5">
-        <v>0.001748139556603662</v>
+        <v>-0.06196438808948766</v>
       </c>
       <c r="Z5">
-        <v>0.166498018382663</v>
+        <v>0.0777809555184685</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05450427132808321</v>
+        <v>0.0601082532285227</v>
       </c>
       <c r="AC5">
-        <v>-0.05450427132808321</v>
+        <v>-0.0601082532285227</v>
       </c>
       <c r="AD5">
-        <v>9238.299999999999</v>
+        <v>114541.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>9238.299999999999</v>
+        <v>114541.5</v>
       </c>
       <c r="AG5">
-        <v>7920.599999999999</v>
+        <v>97702.5</v>
       </c>
       <c r="AH5">
-        <v>0.8430182687569581</v>
+        <v>0.8449561851620436</v>
       </c>
       <c r="AI5">
-        <v>0.7078831624599635</v>
+        <v>0.7151888538396409</v>
       </c>
       <c r="AJ5">
-        <v>0.8215623022746839</v>
+        <v>0.8229651086884192</v>
       </c>
       <c r="AK5">
-        <v>0.6750760681502441</v>
+        <v>0.6817249362600005</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Industrial Bank of Korea (KOSE:A024110)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.0885</v>
-      </c>
-      <c r="E6">
-        <v>0.117</v>
-      </c>
-      <c r="F6">
-        <v>0.0328</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>2204.8</v>
-      </c>
-      <c r="L6">
-        <v>0.3111399621800119</v>
-      </c>
-      <c r="M6">
-        <v>568.5462</v>
-      </c>
-      <c r="N6">
-        <v>0.07736901408450704</v>
-      </c>
-      <c r="O6">
-        <v>0.2578674709724238</v>
-      </c>
-      <c r="P6">
-        <v>568.5462</v>
-      </c>
-      <c r="Q6">
-        <v>0.07736901408450704</v>
-      </c>
-      <c r="R6">
-        <v>0.2578674709724238</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>10521.1</v>
-      </c>
-      <c r="V6">
-        <v>1.431734367558005</v>
-      </c>
-      <c r="W6">
-        <v>0.1149944453426937</v>
-      </c>
-      <c r="X6">
-        <v>0.4448605010984245</v>
-      </c>
-      <c r="Y6">
-        <v>-0.3298660557557307</v>
-      </c>
-      <c r="Z6">
-        <v>0.04333502730225358</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.05484660521633881</v>
-      </c>
-      <c r="AC6">
-        <v>-0.05484660521633881</v>
-      </c>
-      <c r="AD6">
-        <v>180117.3</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>180117.3</v>
-      </c>
-      <c r="AG6">
-        <v>169596.2</v>
-      </c>
-      <c r="AH6">
-        <v>0.9608008500750537</v>
-      </c>
-      <c r="AI6">
-        <v>0.8863185440774414</v>
-      </c>
-      <c r="AJ6">
-        <v>0.9584700756790115</v>
-      </c>
-      <c r="AK6">
-        <v>0.8801116770498992</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>KB Financial Group Inc. (KOSE:A105560)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.0594</v>
-      </c>
-      <c r="E7">
-        <v>0.0667</v>
-      </c>
-      <c r="F7">
-        <v>0.128</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>3511.4</v>
-      </c>
-      <c r="L7">
-        <v>0.3293749061984091</v>
-      </c>
-      <c r="M7">
-        <v>1265</v>
-      </c>
-      <c r="N7">
-        <v>0.07900670151705358</v>
-      </c>
-      <c r="O7">
-        <v>0.36025516887851</v>
-      </c>
-      <c r="P7">
-        <v>987.4</v>
-      </c>
-      <c r="Q7">
-        <v>0.06166894630667091</v>
-      </c>
-      <c r="R7">
-        <v>0.2811983824115737</v>
-      </c>
-      <c r="S7">
-        <v>277.6</v>
-      </c>
-      <c r="T7">
-        <v>0.2194466403162056</v>
-      </c>
-      <c r="U7">
-        <v>20768.4</v>
-      </c>
-      <c r="V7">
-        <v>1.297108916827491</v>
-      </c>
-      <c r="W7">
-        <v>0.1055637895217853</v>
-      </c>
-      <c r="X7">
-        <v>0.1741941301106248</v>
-      </c>
-      <c r="Y7">
-        <v>-0.0686303405888395</v>
-      </c>
-      <c r="Z7">
-        <v>0.07303363474002732</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.05723105259778904</v>
-      </c>
-      <c r="AC7">
-        <v>-0.05723105259778904</v>
-      </c>
-      <c r="AD7">
-        <v>116625.5</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>116625.5</v>
-      </c>
-      <c r="AG7">
-        <v>95857.10000000001</v>
-      </c>
-      <c r="AH7">
-        <v>0.8792846329223867</v>
-      </c>
-      <c r="AI7">
-        <v>0.7273501181841427</v>
-      </c>
-      <c r="AJ7">
-        <v>0.8568737909901277</v>
-      </c>
-      <c r="AK7">
-        <v>0.686780402738034</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Shinhan Financial Group Co., Ltd. (KOSE:A055550)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.453</v>
-      </c>
-      <c r="E8">
-        <v>0.07780000000000001</v>
-      </c>
-      <c r="F8">
-        <v>0.0373</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>3085.6</v>
-      </c>
-      <c r="L8">
-        <v>0.06641297610028238</v>
-      </c>
-      <c r="M8">
-        <v>1508.6</v>
-      </c>
-      <c r="N8">
-        <v>0.09431048818149423</v>
-      </c>
-      <c r="O8">
-        <v>0.4889162561576355</v>
-      </c>
-      <c r="P8">
-        <v>1036.5</v>
-      </c>
-      <c r="Q8">
-        <v>0.06479704427954314</v>
-      </c>
-      <c r="R8">
-        <v>0.3359152190821882</v>
-      </c>
-      <c r="S8">
-        <v>472.0999999999999</v>
-      </c>
-      <c r="T8">
-        <v>0.312939148879756</v>
-      </c>
-      <c r="U8">
-        <v>22821</v>
-      </c>
-      <c r="V8">
-        <v>1.426660248435556</v>
-      </c>
-      <c r="W8">
-        <v>0.09135994741532713</v>
-      </c>
-      <c r="X8">
-        <v>0.1673490487586974</v>
-      </c>
-      <c r="Y8">
-        <v>-0.07598910134337025</v>
-      </c>
-      <c r="Z8">
-        <v>0.3450904194120789</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.05725024348008073</v>
-      </c>
-      <c r="AC8">
-        <v>-0.05725024348008073</v>
-      </c>
-      <c r="AD8">
-        <v>109545.9</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>109545.9</v>
-      </c>
-      <c r="AG8">
-        <v>86724.89999999999</v>
-      </c>
-      <c r="AH8">
-        <v>0.8725836771757658</v>
-      </c>
-      <c r="AI8">
-        <v>0.7232905637255711</v>
-      </c>
-      <c r="AJ8">
-        <v>0.8442762434166333</v>
-      </c>
-      <c r="AK8">
-        <v>0.674199413995844</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>KakaoBank Corp. (KOSE:A323410)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="F9">
-        <v>0.373</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>252.4</v>
-      </c>
-      <c r="L9">
-        <v>0.2673445609575257</v>
-      </c>
-      <c r="M9">
-        <v>9.66</v>
-      </c>
-      <c r="N9">
-        <v>0.0009148333696362449</v>
-      </c>
-      <c r="O9">
-        <v>0.03827258320126783</v>
-      </c>
-      <c r="P9">
-        <v>-0</v>
-      </c>
-      <c r="Q9">
-        <v>-0</v>
-      </c>
-      <c r="R9">
-        <v>-0</v>
-      </c>
-      <c r="S9">
-        <v>9.66</v>
-      </c>
-      <c r="T9">
-        <v>1</v>
-      </c>
-      <c r="U9">
-        <v>15.8</v>
-      </c>
-      <c r="V9">
-        <v>0.001496311308514769</v>
-      </c>
-      <c r="W9">
-        <v>0.06457720353076628</v>
-      </c>
-      <c r="X9">
-        <v>0.05974923784319833</v>
-      </c>
-      <c r="Y9">
-        <v>0.004827965687567951</v>
-      </c>
-      <c r="Z9">
-        <v>0.2418896136837628</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.05974923784319833</v>
-      </c>
-      <c r="AC9">
-        <v>-0.05974923784319833</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>-15.8</v>
-      </c>
-      <c r="AH9">
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <v>0</v>
-      </c>
-      <c r="AJ9">
-        <v>-0.001498553611229668</v>
-      </c>
-      <c r="AK9">
-        <v>-0.003577979573812813</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/south_korea/south_korea_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0623</v>
+        <v>0.06494999999999999</v>
       </c>
       <c r="E2">
-        <v>0.09390000000000001</v>
+        <v>0.09205000000000001</v>
       </c>
       <c r="F2">
-        <v>0.09759999999999999</v>
+        <v>0.112</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>9130.299999999999</v>
+        <v>14828.6</v>
       </c>
       <c r="L2">
-        <v>0.3168416815307843</v>
+        <v>0.3104282765521833</v>
       </c>
       <c r="M2">
-        <v>4120.0526</v>
+        <v>7342.7508</v>
       </c>
       <c r="N2">
-        <v>0.09156791607863184</v>
+        <v>0.101264795119045</v>
       </c>
       <c r="O2">
-        <v>0.4512505175076394</v>
+        <v>0.4951749187381141</v>
       </c>
       <c r="P2">
-        <v>2758.5526</v>
+        <v>4709.1508</v>
       </c>
       <c r="Q2">
-        <v>0.06130866216982075</v>
+        <v>0.06494448796310599</v>
       </c>
       <c r="R2">
-        <v>0.3021316495624459</v>
+        <v>0.3175721780882889</v>
       </c>
       <c r="S2">
-        <v>1361.5</v>
+        <v>2633.6</v>
       </c>
       <c r="T2">
-        <v>0.330456946107921</v>
+        <v>0.3586666729858243</v>
       </c>
       <c r="U2">
-        <v>58529.3</v>
+        <v>95067.3</v>
       </c>
       <c r="V2">
-        <v>1.300810099012102</v>
+        <v>1.311085030561133</v>
       </c>
       <c r="W2">
-        <v>0.08781607232975217</v>
+        <v>0.08852235434513915</v>
       </c>
       <c r="X2">
-        <v>0.1746496738443003</v>
+        <v>0.1745860279803974</v>
       </c>
       <c r="Y2">
-        <v>-0.08683360151454811</v>
+        <v>-0.08606367363525826</v>
       </c>
       <c r="Z2">
-        <v>0.06302290634614068</v>
+        <v>0.07178089906972837</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05987982846021396</v>
+        <v>0.06010059783600637</v>
       </c>
       <c r="AC2">
-        <v>-0.05987982846021396</v>
+        <v>-0.06010059783600637</v>
       </c>
       <c r="AD2">
-        <v>424344.3</v>
+        <v>607199.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>424344.3</v>
+        <v>607199.3</v>
       </c>
       <c r="AG2">
-        <v>365815</v>
+        <v>512132.0000000001</v>
       </c>
       <c r="AH2">
-        <v>0.9041321535743476</v>
+        <v>0.8933215165238925</v>
       </c>
       <c r="AI2">
-        <v>0.7852675645256741</v>
+        <v>0.7663064315546978</v>
       </c>
       <c r="AJ2">
-        <v>0.8904735649978883</v>
+        <v>0.8759747839020914</v>
       </c>
       <c r="AK2">
-        <v>0.7591846052474565</v>
+        <v>0.7344457031014159</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Industrial Bank of Korea (KOSE:A024110)</t>
+          <t>Woori Financial Group Inc. (KOSE:A316140)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.06759999999999999</v>
+        <v>0.0779</v>
       </c>
       <c r="E3">
-        <v>0.106</v>
+        <v>0.0873</v>
       </c>
       <c r="F3">
-        <v>0.015</v>
+        <v>0.112</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2091.8</v>
+        <v>2077</v>
       </c>
       <c r="L3">
-        <v>0.3120273273766017</v>
+        <v>0.2744631648496861</v>
       </c>
       <c r="M3">
-        <v>597.2526</v>
+        <v>1453.6</v>
       </c>
       <c r="N3">
-        <v>0.07720232155321735</v>
+        <v>0.1881317543519058</v>
       </c>
       <c r="O3">
-        <v>0.2855208910985754</v>
+        <v>0.6998555609051517</v>
       </c>
       <c r="P3">
-        <v>597.2526</v>
+        <v>807.2</v>
       </c>
       <c r="Q3">
-        <v>0.07720232155321735</v>
+        <v>0.1044716236329515</v>
       </c>
       <c r="R3">
-        <v>0.2855208910985754</v>
+        <v>0.3886374578719307</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>646.3999999999999</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.4446890478811227</v>
       </c>
       <c r="U3">
-        <v>11575.8</v>
+        <v>13834.1</v>
       </c>
       <c r="V3">
-        <v>1.496316020785398</v>
+        <v>1.790474341551802</v>
       </c>
       <c r="W3">
-        <v>0.09170458829821747</v>
+        <v>0.08852235434513915</v>
       </c>
       <c r="X3">
-        <v>0.4263406632787151</v>
+        <v>0.1955917479742204</v>
       </c>
       <c r="Y3">
-        <v>-0.3346360749804976</v>
+        <v>-0.1070693936290812</v>
       </c>
       <c r="Z3">
-        <v>0.03481225301573949</v>
+        <v>0.09408615519273519</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05829540398678958</v>
+        <v>0.05807896313921694</v>
       </c>
       <c r="AC3">
-        <v>-0.05829540398678958</v>
+        <v>-0.05807896313921694</v>
       </c>
       <c r="AD3">
-        <v>189456</v>
+        <v>68273.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>189456</v>
+        <v>68273.8</v>
       </c>
       <c r="AG3">
-        <v>177880.2</v>
+        <v>54439.7</v>
       </c>
       <c r="AH3">
-        <v>0.9607682251123523</v>
+        <v>0.8983359276213383</v>
       </c>
       <c r="AI3">
-        <v>0.8806356923892151</v>
+        <v>0.7123912873353333</v>
       </c>
       <c r="AJ3">
-        <v>0.9583215707232765</v>
+        <v>0.8757122037377224</v>
       </c>
       <c r="AK3">
-        <v>0.8738478195831493</v>
+        <v>0.6638712541187316</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shinhan Financial Group Co., Ltd. (KOSE:A055550)</t>
+          <t>Industrial Bank of Korea (KOSE:A024110)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0599</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="E4">
-        <v>0.06150000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="F4">
-        <v>0.09759999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3497.6</v>
+        <v>2091.8</v>
       </c>
       <c r="L4">
-        <v>0.3076138292539203</v>
+        <v>0.3120273273766017</v>
       </c>
       <c r="M4">
-        <v>1529.3</v>
+        <v>597.2526</v>
       </c>
       <c r="N4">
-        <v>0.09416466039025412</v>
+        <v>0.07720232155321735</v>
       </c>
       <c r="O4">
-        <v>0.437242680695334</v>
+        <v>0.2855208910985754</v>
       </c>
       <c r="P4">
-        <v>958.1</v>
+        <v>597.2526</v>
       </c>
       <c r="Q4">
-        <v>0.05899376258412507</v>
+        <v>0.07720232155321735</v>
       </c>
       <c r="R4">
-        <v>0.2739306953339433</v>
+        <v>0.2855208910985754</v>
       </c>
       <c r="S4">
-        <v>571.2000000000002</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.3735042176159027</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>30114.5</v>
+        <v>11575.8</v>
       </c>
       <c r="V4">
-        <v>1.854261207952859</v>
+        <v>1.496316020785398</v>
       </c>
       <c r="W4">
-        <v>0.08781607232975217</v>
+        <v>0.09170458829821747</v>
       </c>
       <c r="X4">
-        <v>0.1746496738443003</v>
+        <v>0.4261526935420294</v>
       </c>
       <c r="Y4">
-        <v>-0.08683360151454811</v>
+        <v>-0.334448105243812</v>
       </c>
       <c r="Z4">
-        <v>0.0898441450895115</v>
+        <v>0.03481225301573949</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05987982846021396</v>
+        <v>0.05828802960039423</v>
       </c>
       <c r="AC4">
-        <v>-0.05987982846021396</v>
+        <v>-0.05828802960039423</v>
       </c>
       <c r="AD4">
-        <v>120346.8</v>
+        <v>189456</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>120346.8</v>
+        <v>189456</v>
       </c>
       <c r="AG4">
-        <v>90232.3</v>
+        <v>177880.2</v>
       </c>
       <c r="AH4">
-        <v>0.8810967328635491</v>
+        <v>0.9607682251123523</v>
       </c>
       <c r="AI4">
-        <v>0.7289738307487944</v>
+        <v>0.8806356923892151</v>
       </c>
       <c r="AJ4">
-        <v>0.8474664938529017</v>
+        <v>0.9583215707232765</v>
       </c>
       <c r="AK4">
-        <v>0.6685052624092247</v>
+        <v>0.8738478195831493</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,120 +954,611 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Shinhan Financial Group Co., Ltd. (KOSE:A055550)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0599</v>
+      </c>
+      <c r="E5">
+        <v>0.06150000000000001</v>
+      </c>
+      <c r="F5">
+        <v>0.09759999999999999</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>3497.6</v>
+      </c>
+      <c r="L5">
+        <v>0.3076138292539203</v>
+      </c>
+      <c r="M5">
+        <v>1529.3</v>
+      </c>
+      <c r="N5">
+        <v>0.09416466039025412</v>
+      </c>
+      <c r="O5">
+        <v>0.437242680695334</v>
+      </c>
+      <c r="P5">
+        <v>958.1</v>
+      </c>
+      <c r="Q5">
+        <v>0.05899376258412507</v>
+      </c>
+      <c r="R5">
+        <v>0.2739306953339433</v>
+      </c>
+      <c r="S5">
+        <v>571.2000000000002</v>
+      </c>
+      <c r="T5">
+        <v>0.3735042176159027</v>
+      </c>
+      <c r="U5">
+        <v>30114.5</v>
+      </c>
+      <c r="V5">
+        <v>1.854261207952859</v>
+      </c>
+      <c r="W5">
+        <v>0.08781607232975217</v>
+      </c>
+      <c r="X5">
+        <v>0.1745860279803974</v>
+      </c>
+      <c r="Y5">
+        <v>-0.08676995565064524</v>
+      </c>
+      <c r="Z5">
+        <v>0.0898441450895115</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.05987226075905619</v>
+      </c>
+      <c r="AC5">
+        <v>-0.05987226075905619</v>
+      </c>
+      <c r="AD5">
+        <v>120346.8</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>120346.8</v>
+      </c>
+      <c r="AG5">
+        <v>90232.3</v>
+      </c>
+      <c r="AH5">
+        <v>0.8810967328635491</v>
+      </c>
+      <c r="AI5">
+        <v>0.7289738307487944</v>
+      </c>
+      <c r="AJ5">
+        <v>0.8474664938529017</v>
+      </c>
+      <c r="AK5">
+        <v>0.6685052624092247</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>KB Financial Group Inc. (KOSE:A105560)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>0.0623</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>0.09390000000000001</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>0.122</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>3540.9</v>
       </c>
-      <c r="L5">
+      <c r="L6">
         <v>0.3296129428629941</v>
       </c>
-      <c r="M5">
+      <c r="M6">
         <v>1993.5</v>
       </c>
-      <c r="N5">
+      <c r="N6">
         <v>0.09484907886723509</v>
       </c>
-      <c r="O5">
+      <c r="O6">
         <v>0.5629924595441836</v>
       </c>
-      <c r="P5">
+      <c r="P6">
         <v>1203.2</v>
       </c>
-      <c r="Q5">
+      <c r="Q6">
         <v>0.05724725943970768</v>
       </c>
-      <c r="R5">
+      <c r="R6">
         <v>0.3398006156626847</v>
       </c>
-      <c r="S5">
+      <c r="S6">
         <v>790.3</v>
       </c>
-      <c r="T5">
+      <c r="T6">
         <v>0.3964384248808628</v>
       </c>
-      <c r="U5">
+      <c r="U6">
         <v>16839</v>
       </c>
-      <c r="V5">
+      <c r="V6">
         <v>0.8011856729598051</v>
       </c>
-      <c r="W5">
+      <c r="W6">
         <v>0.08379559072708513</v>
       </c>
-      <c r="X5">
-        <v>0.1457599788165728</v>
-      </c>
-      <c r="Y5">
-        <v>-0.06196438808948766</v>
-      </c>
-      <c r="Z5">
+      <c r="X6">
+        <v>0.1457106031447711</v>
+      </c>
+      <c r="Y6">
+        <v>-0.06191501241768595</v>
+      </c>
+      <c r="Z6">
         <v>0.0777809555184685</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.0601082532285227</v>
-      </c>
-      <c r="AC5">
-        <v>-0.0601082532285227</v>
-      </c>
-      <c r="AD5">
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06010059783600637</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06010059783600637</v>
+      </c>
+      <c r="AD6">
         <v>114541.5</v>
       </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
         <v>114541.5</v>
       </c>
-      <c r="AG5">
+      <c r="AG6">
         <v>97702.5</v>
       </c>
-      <c r="AH5">
+      <c r="AH6">
         <v>0.8449561851620436</v>
       </c>
-      <c r="AI5">
+      <c r="AI6">
         <v>0.7151888538396409</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ6">
         <v>0.8229651086884192</v>
       </c>
-      <c r="AK5">
+      <c r="AK6">
         <v>0.6817249362600005</v>
       </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hana Financial Group Inc. (KOSE:A086790)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>-0.0611</v>
+      </c>
+      <c r="E7">
+        <v>0.0902</v>
+      </c>
+      <c r="F7">
+        <v>0.07440000000000001</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>2793.6</v>
+      </c>
+      <c r="L7">
+        <v>0.3317460128964838</v>
+      </c>
+      <c r="M7">
+        <v>1590.35</v>
+      </c>
+      <c r="N7">
+        <v>0.1461906863015461</v>
+      </c>
+      <c r="O7">
+        <v>0.5692833619702177</v>
+      </c>
+      <c r="P7">
+        <v>990.1499999999999</v>
+      </c>
+      <c r="Q7">
+        <v>0.09101814571727979</v>
+      </c>
+      <c r="R7">
+        <v>0.3544351374570446</v>
+      </c>
+      <c r="S7">
+        <v>600.2</v>
+      </c>
+      <c r="T7">
+        <v>0.3774012009934921</v>
+      </c>
+      <c r="U7">
+        <v>19262.2</v>
+      </c>
+      <c r="V7">
+        <v>1.770650635192028</v>
+      </c>
+      <c r="W7">
+        <v>0.09548647309144977</v>
+      </c>
+      <c r="X7">
+        <v>0.2054557495004286</v>
+      </c>
+      <c r="Y7">
+        <v>-0.1099692764089789</v>
+      </c>
+      <c r="Z7">
+        <v>0.0752816502262678</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.06040101193282939</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06040101193282939</v>
+      </c>
+      <c r="AD7">
+        <v>103412</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>103412</v>
+      </c>
+      <c r="AG7">
+        <v>84149.8</v>
+      </c>
+      <c r="AH7">
+        <v>0.9048163191023584</v>
+      </c>
+      <c r="AI7">
+        <v>0.7609441087390986</v>
+      </c>
+      <c r="AJ7">
+        <v>0.8855226437570242</v>
+      </c>
+      <c r="AK7">
+        <v>0.7214649846447195</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JB Financial Group Co., Ltd. (KOSE:A175330)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0823</v>
+      </c>
+      <c r="E8">
+        <v>0.151</v>
+      </c>
+      <c r="F8">
+        <v>0.124</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>499.3</v>
+      </c>
+      <c r="L8">
+        <v>0.2754454680862801</v>
+      </c>
+      <c r="M8">
+        <v>178.7482</v>
+      </c>
+      <c r="N8">
+        <v>0.08457049583648753</v>
+      </c>
+      <c r="O8">
+        <v>0.3579975966352895</v>
+      </c>
+      <c r="P8">
+        <v>153.2482</v>
+      </c>
+      <c r="Q8">
+        <v>0.07250577214231645</v>
+      </c>
+      <c r="R8">
+        <v>0.3069260965351492</v>
+      </c>
+      <c r="S8">
+        <v>25.5</v>
+      </c>
+      <c r="T8">
+        <v>0.1426587792212733</v>
+      </c>
+      <c r="U8">
+        <v>1593.4</v>
+      </c>
+      <c r="V8">
+        <v>0.75387963663891</v>
+      </c>
+      <c r="W8">
+        <v>0.1363239228963032</v>
+      </c>
+      <c r="X8">
+        <v>0.1432751721241914</v>
+      </c>
+      <c r="Y8">
+        <v>-0.006951249227888173</v>
+      </c>
+      <c r="Z8">
+        <v>0.1572691543540313</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.06075702842736069</v>
+      </c>
+      <c r="AC8">
+        <v>-0.06075702842736069</v>
+      </c>
+      <c r="AD8">
+        <v>11169.2</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>11169.2</v>
+      </c>
+      <c r="AG8">
+        <v>9575.800000000001</v>
+      </c>
+      <c r="AH8">
+        <v>0.8408769235402174</v>
+      </c>
+      <c r="AI8">
+        <v>0.7278627844537706</v>
+      </c>
+      <c r="AJ8">
+        <v>0.8191866135130973</v>
+      </c>
+      <c r="AK8">
+        <v>0.6963306621678617</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KakaoBank Corp. (KOSE:A323410)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>0.292</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>328.4</v>
+      </c>
+      <c r="L9">
+        <v>0.2854411125597566</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>-0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1848.3</v>
+      </c>
+      <c r="V9">
+        <v>0.2719207909139058</v>
+      </c>
+      <c r="W9">
+        <v>0.07410248888688313</v>
+      </c>
+      <c r="X9">
+        <v>0.06543905665141708</v>
+      </c>
+      <c r="Y9">
+        <v>0.008663432235466048</v>
+      </c>
+      <c r="Z9">
+        <v>0.2605357911184583</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.06543905665141708</v>
+      </c>
+      <c r="AC9">
+        <v>-0.06543905665141708</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>-1848.3</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.3734769342682213</v>
+      </c>
+      <c r="AK9">
+        <v>-0.6042170644001308</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
         <v>0</v>
       </c>
     </row>
